--- a/data/trans_orig/P78A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76113</t>
+          <t>75748</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107494</t>
+          <t>108015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127717</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138763</t>
+          <t>139108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205626</t>
+          <t>206879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242269</t>
+          <t>242387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42111</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>20911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24531</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61174</t>
+          <t>59921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204682</t>
+          <t>206521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249759</t>
+          <t>250176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240021</t>
+          <t>240999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>273304</t>
+          <t>274603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461483</t>
+          <t>459887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>515941</t>
+          <t>514159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71316</t>
+          <t>69477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81060</t>
+          <t>79761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114343</t>
+          <t>113365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114421</t>
+          <t>116203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168879</t>
+          <t>170475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125418</t>
+          <t>125725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149248</t>
+          <t>149166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180869</t>
+          <t>181633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202822</t>
+          <t>202201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314049</t>
+          <t>315321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345897</t>
+          <t>345970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37378</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48705</t>
+          <t>47941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46473</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78321</t>
+          <t>77049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101309</t>
+          <t>103164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>138685</t>
+          <t>140253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157076</t>
+          <t>157826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>184522</t>
+          <t>184052</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>272586</t>
+          <t>273329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316783</t>
+          <t>316353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>43566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37660</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65106</t>
+          <t>64356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52130</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96327</t>
+          <t>95584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55397</t>
+          <t>55735</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69856</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84567</t>
+          <t>85257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117281</t>
+          <t>117317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137306</t>
+          <t>137154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30639</t>
+          <t>29760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45415</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111416</t>
+          <t>110441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127555</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122639</t>
+          <t>123974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>143980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>241066</t>
+          <t>241745</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>267450</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50847</t>
+          <t>49512</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39784</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66168</t>
+          <t>65489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>211612</t>
+          <t>211948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>254877</t>
+          <t>256022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>410855</t>
+          <t>414404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>507471</t>
+          <t>509843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>650180</t>
+          <t>647260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>771157</t>
+          <t>767609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>30596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75006</t>
+          <t>74670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>22794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121782</t>
+          <t>118233</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48098</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>169075</t>
+          <t>171995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>236551</t>
+          <t>237951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>266556</t>
+          <t>268725</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>295164</t>
+          <t>294009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>329450</t>
+          <t>329169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>543154</t>
+          <t>544282</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>588978</t>
+          <t>589535</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60583</t>
+          <t>59183</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115216</t>
+          <t>115497</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149502</t>
+          <t>150657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152822</t>
+          <t>152265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>198646</t>
+          <t>197518</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1202066</t>
+          <t>1194297</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1290581</t>
+          <t>1289961</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1683269</t>
+          <t>1685046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1878105</t>
+          <t>1862130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2933330</t>
+          <t>2926382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3136524</t>
+          <t>3123572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>192867</t>
+          <t>193487</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>281382</t>
+          <t>289151</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>327875</t>
+          <t>343850</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>522711</t>
+          <t>520934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>552904</t>
+          <t>565856</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>756098</t>
+          <t>763046</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94196</t>
+          <t>102052</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75748</t>
+          <t>89664</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108015</t>
+          <t>110316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>134515</t>
+          <t>145267</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127665</t>
+          <t>134903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139108</t>
+          <t>152707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>228711</t>
+          <t>247319</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206879</t>
+          <t>231006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242387</t>
+          <t>258255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20911</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38089</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>52717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>118224</t>
+          <t>117376</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118224</t>
+          <t>117376</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118224</t>
+          <t>117376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>148576</t>
+          <t>166347</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148576</t>
+          <t>166347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148576</t>
+          <t>166347</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>266800</t>
+          <t>283723</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>266800</t>
+          <t>283723</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>266800</t>
+          <t>283723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>231588</t>
+          <t>237725</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206521</t>
+          <t>214489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250176</t>
+          <t>255005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,67 +1103,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>257562</t>
+          <t>269995</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240999</t>
+          <t>251796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>274603</t>
+          <t>287712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>507720</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>479925</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>531681</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>77,49%</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>489150</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>459887</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>514159</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>77,6%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44410</t>
+          <t>40498</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>23218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69477</t>
+          <t>63734</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,67 +1216,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>96802</t>
+          <t>106997</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79761</t>
+          <t>89280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113365</t>
+          <t>125196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>33,21%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>147495</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>123534</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>175290</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>31,99%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>141212</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>116203</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>170475</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>278223</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>278223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>278223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>354364</t>
+          <t>376992</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>354364</t>
+          <t>376992</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>354364</t>
+          <t>376992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>630362</t>
+          <t>655215</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>630362</t>
+          <t>655215</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>630362</t>
+          <t>655215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>138470</t>
+          <t>140438</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125725</t>
+          <t>128891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149166</t>
+          <t>148956</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>192964</t>
+          <t>196554</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181633</t>
+          <t>184901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202201</t>
+          <t>204953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>331435</t>
+          <t>336992</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>315321</t>
+          <t>320753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345970</t>
+          <t>351053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>33277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36610</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47941</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>59883</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46400</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77049</t>
+          <t>76122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>162796</t>
+          <t>162168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162796</t>
+          <t>162168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162796</t>
+          <t>162168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>229574</t>
+          <t>234707</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>229574</t>
+          <t>234707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229574</t>
+          <t>234707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>392370</t>
+          <t>396875</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>392370</t>
+          <t>396875</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>392370</t>
+          <t>396875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126787</t>
+          <t>142936</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103164</t>
+          <t>123066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140253</t>
+          <t>155604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>188623</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157826</t>
+          <t>171240</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>184052</t>
+          <t>202568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>298808</t>
+          <t>331559</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273329</t>
+          <t>305992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316353</t>
+          <t>351994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43566</t>
+          <t>40408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50162</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38130</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64356</t>
+          <t>75531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>70105</t>
+          <t>78686</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>58251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95584</t>
+          <t>104253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>146730</t>
+          <t>163474</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146730</t>
+          <t>163474</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>146730</t>
+          <t>163474</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>222182</t>
+          <t>246771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>222182</t>
+          <t>246771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>222182</t>
+          <t>246771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>368913</t>
+          <t>410245</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>368913</t>
+          <t>410245</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>368913</t>
+          <t>410245</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>53185</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>44412</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55735</t>
+          <t>59691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>78780</t>
+          <t>82811</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70735</t>
+          <t>74452</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85257</t>
+          <t>89779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>128686</t>
+          <t>135996</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117317</t>
+          <t>124162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137154</t>
+          <t>145380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>37979</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>28595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>49813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62200</t>
+          <t>67288</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62200</t>
+          <t>67288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62200</t>
+          <t>67288</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100495</t>
+          <t>106687</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100495</t>
+          <t>106687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100495</t>
+          <t>106687</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>162696</t>
+          <t>173975</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162696</t>
+          <t>173975</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162696</t>
+          <t>173975</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>121647</t>
+          <t>122848</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110441</t>
+          <t>114650</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127575</t>
+          <t>128611</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>134047</t>
+          <t>138176</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123974</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143980</t>
+          <t>147446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>255694</t>
+          <t>261024</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>241745</t>
+          <t>247289</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>268134</t>
+          <t>271780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39439</t>
+          <t>41356</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49512</t>
+          <t>52532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>51540</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>41703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65489</t>
+          <t>66194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>133747</t>
+          <t>133951</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133747</t>
+          <t>133951</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133747</t>
+          <t>133951</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>173486</t>
+          <t>179532</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>173486</t>
+          <t>179532</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>173486</t>
+          <t>179532</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>307234</t>
+          <t>313483</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>307234</t>
+          <t>313483</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>307234</t>
+          <t>313483</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>235806</t>
+          <t>279797</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>211948</t>
+          <t>253057</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256022</t>
+          <t>297561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>464275</t>
+          <t>320942</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>414404</t>
+          <t>299943</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>509843</t>
+          <t>336862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>700081</t>
+          <t>600739</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>647260</t>
+          <t>570765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>767609</t>
+          <t>625536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>48706</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30596</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74670</t>
+          <t>75446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68362</t>
+          <t>77325</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>61405</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118233</t>
+          <t>98324</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>126031</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51646</t>
+          <t>101234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>171995</t>
+          <t>156005</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>286618</t>
+          <t>328503</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>286618</t>
+          <t>328503</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>286618</t>
+          <t>328503</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>532637</t>
+          <t>398267</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>532637</t>
+          <t>398267</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>532637</t>
+          <t>398267</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>819255</t>
+          <t>726770</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>819255</t>
+          <t>726770</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>819255</t>
+          <t>726770</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>253469</t>
+          <t>282497</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>237951</t>
+          <t>259942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>268725</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>312651</t>
+          <t>362455</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>294009</t>
+          <t>342920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>329169</t>
+          <t>382224</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>566120</t>
+          <t>644952</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>544282</t>
+          <t>617776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>589535</t>
+          <t>669762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>43665</t>
+          <t>56949</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>39215</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>79504</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>132015</t>
+          <t>156918</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115497</t>
+          <t>137149</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>150657</t>
+          <t>176453</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>175680</t>
+          <t>213867</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152265</t>
+          <t>189057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>197518</t>
+          <t>241043</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>297134</t>
+          <t>339446</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>297134</t>
+          <t>339446</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>297134</t>
+          <t>339446</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>444666</t>
+          <t>519373</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>444666</t>
+          <t>519373</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>444666</t>
+          <t>519373</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>741800</t>
+          <t>858819</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>741800</t>
+          <t>858819</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>741800</t>
+          <t>858819</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1251869</t>
+          <t>1361478</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1194297</t>
+          <t>1317882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1289961</t>
+          <t>1400476</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1746814</t>
+          <t>1704824</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1685046</t>
+          <t>1656945</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1862130</t>
+          <t>1741603</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2998684</t>
+          <t>3066302</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2926382</t>
+          <t>3006077</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3123572</t>
+          <t>3123037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>231579</t>
+          <t>228952</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>193487</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>289151</t>
+          <t>272548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>459166</t>
+          <t>523852</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>343850</t>
+          <t>487073</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>520934</t>
+          <t>571731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>690744</t>
+          <t>752804</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>565856</t>
+          <t>696069</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>763046</t>
+          <t>813029</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
